--- a/artfynd/A 31015-2024 artfynd.xlsx
+++ b/artfynd/A 31015-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120023532</v>
+        <v>120023552</v>
       </c>
       <c r="B2" t="n">
-        <v>5169</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Söderviken, Söderviken, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>702156</v>
+        <v>702149</v>
       </c>
       <c r="R2" t="n">
-        <v>6603900</v>
+        <v>6603907</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -755,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120023926</v>
+        <v>120023901</v>
       </c>
       <c r="B3" t="n">
-        <v>57336</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,56 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Nynäsudden, Nynäsudden, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>702078</v>
+        <v>702073</v>
       </c>
       <c r="R3" t="n">
-        <v>6603864</v>
+        <v>6603870</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,37 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120024413</v>
+        <v>120023995</v>
       </c>
       <c r="B4" t="n">
-        <v>90600</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>4217</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -969,7 +930,7 @@
         <v>6603884</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,15 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120023901</v>
+        <v>120024413</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1075,13 +1031,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>702073</v>
+        <v>702082</v>
       </c>
       <c r="R5" t="n">
-        <v>6603870</v>
+        <v>6603884</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,43 +1103,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120023060</v>
+        <v>120023210</v>
       </c>
       <c r="B6" t="n">
-        <v>43686</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101735</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1192,13 +1147,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>701849</v>
+        <v>702074</v>
       </c>
       <c r="R6" t="n">
-        <v>6603796</v>
+        <v>6603734</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1227,7 +1182,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1192,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,15 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120023579</v>
+        <v>120023926</v>
       </c>
       <c r="B7" t="n">
-        <v>5189</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,16 +1230,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1297,25 +1247,39 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Söderviken, Söderviken, Upl</t>
+          <t>Nynäsudden, Nynäsudden, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>702139</v>
+        <v>702078</v>
       </c>
       <c r="R7" t="n">
-        <v>6603921</v>
+        <v>6603864</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1344,7 +1308,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,7 +1318,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,15 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120023613</v>
+        <v>120023532</v>
       </c>
       <c r="B8" t="n">
-        <v>5169</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1422,14 +1381,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nynäsudden, Nynäsudden, Upl</t>
+          <t>Söderviken, Söderviken, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>702123</v>
+        <v>702156</v>
       </c>
       <c r="R8" t="n">
-        <v>6603926</v>
+        <v>6603900</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1461,7 +1420,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1430,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,15 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120023995</v>
+        <v>120023613</v>
       </c>
       <c r="B9" t="n">
-        <v>90975</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,34 +1468,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4217</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Nynäsudden, Nynäsudden, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>702082</v>
+        <v>702123</v>
       </c>
       <c r="R9" t="n">
-        <v>6603884</v>
+        <v>6603926</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1573,7 +1532,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,7 +1542,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,50 +1569,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120023552</v>
+        <v>120023060</v>
       </c>
       <c r="B10" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>44177</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>101735</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Söderviken, Söderviken, Upl</t>
+          <t>Nynäsudden, Nynäsudden, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>702149</v>
+        <v>701849</v>
       </c>
       <c r="R10" t="n">
-        <v>6603907</v>
+        <v>6603796</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1685,7 +1644,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,7 +1654,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,6 +1678,230 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120023579</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Söderviken, Söderviken, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>702139</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6603921</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ljusterö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120026648</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nynäsudden, Nynäsudden, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>702003</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6603750</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ljusterö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-09-26</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31015-2024 artfynd.xlsx
+++ b/artfynd/A 31015-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120023552</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120023901</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120023995</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120024413</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1216,6 +1241,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120023210</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1342,6 +1372,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120023926</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1454,6 +1489,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120023532</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1566,6 +1606,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120023613</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1678,6 +1723,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120023060</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1790,6 +1840,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120023579</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1902,8 +1957,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120026648</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>